--- a/output/pdf_financials_xlsx/ADR.H.xlsx
+++ b/output/pdf_financials_xlsx/ADR.H.xlsx
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.018156</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000376</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.398037</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.018782</v>
@@ -2231,34 +2231,34 @@
         <v>0.023861</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.006053</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.013633</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.014282</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.00851</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003954</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.275537</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.236219</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.093872</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.023358</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.002269</v>
       </c>
     </row>
     <row r="35">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.018156</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000376</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.398037</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.321009</v>
@@ -2335,34 +2335,34 @@
         <v>0.245837</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.196476</v>
+        <v>0.202529</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.141091</v>
+        <v>0.154724</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.090394</v>
+        <v>0.104676</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.050209</v>
+        <v>0.058719</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.010054</v>
+        <v>0.014008</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.275537</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.236219</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.093872</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.023358</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.002269</v>
       </c>
     </row>
     <row r="37">
@@ -2944,13 +2944,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.018594</v>
+        <v>0.000438</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.000843</v>
+        <v>0.000467</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.398999</v>
+        <v>0.000962</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">

--- a/output/pdf_financials_xlsx/ADR.H.xlsx
+++ b/output/pdf_financials_xlsx/ADR.H.xlsx
@@ -1027,10 +1027,10 @@
         <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.000351</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.001886</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>-0</v>
@@ -1051,19 +1051,19 @@
         <v>-0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>0.006418</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>0.000218</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>0.000322</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>0.0005</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>0.001827</v>
       </c>
     </row>
     <row r="14">
@@ -1843,10 +1843,10 @@
         <v>-0.050619</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.06954100000000001</v>
+        <v>-0.069892</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.103569</v>
+        <v>-0.101683</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.07760300000000001</v>
@@ -1867,19 +1867,19 @@
         <v>-0.044029</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.122758</v>
+        <v>-0.129176</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.054658</v>
+        <v>-0.054876</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.128411</v>
+        <v>-0.128733</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.072794</v>
+        <v>-0.073294</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.155384</v>
+        <v>-0.157211</v>
       </c>
     </row>
     <row r="28">
@@ -1947,10 +1947,10 @@
         <v>-0.050619</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.06954100000000001</v>
+        <v>-0.069892</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.103569</v>
+        <v>-0.101683</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.07760300000000001</v>
@@ -1971,19 +1971,19 @@
         <v>-0.044029</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.122758</v>
+        <v>-0.129176</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.054658</v>
+        <v>-0.054876</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.128411</v>
+        <v>-0.128733</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.072794</v>
+        <v>-0.073294</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.155384</v>
+        <v>-0.157211</v>
       </c>
     </row>
     <row r="30">
@@ -20385,7 +20385,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
